--- a/data/trans_orig/P6712-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6712-Habitat-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo requiere que tenga iniciativa en 2012</t>
+          <t>Población según si su trabajo requiere que tenga iniciativa en 2012 (tasa de respuesta: 99,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17176</t>
+          <t>17498</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14794</t>
+          <t>14020</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10350</t>
+          <t>9998</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26852</t>
+          <t>26143</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8650</t>
+          <t>9048</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25717</t>
+          <t>25216</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19336</t>
+          <t>20684</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16836</t>
+          <t>17619</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>39273</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27088</t>
+          <t>26948</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50970</t>
+          <t>50874</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10595</t>
+          <t>10221</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26202</t>
+          <t>26206</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41401</t>
+          <t>41188</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>69285</t>
+          <t>69796</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39608</t>
+          <t>38354</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64848</t>
+          <t>64197</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36196</t>
+          <t>36320</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60509</t>
+          <t>60760</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82741</t>
+          <t>82454</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116381</t>
+          <t>116613</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,17%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>139173</t>
+          <t>138654</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>171449</t>
+          <t>173086</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64896</t>
+          <t>65130</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90808</t>
+          <t>91031</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>212387</t>
+          <t>214862</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>251962</t>
+          <t>254974</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>59,41%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13352</t>
+          <t>13152</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32602</t>
+          <t>31378</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7267</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21505</t>
+          <t>20871</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22965</t>
+          <t>23742</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46778</t>
+          <t>46640</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>10640</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28171</t>
+          <t>27385</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5255</t>
+          <t>5679</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18265</t>
+          <t>19310</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18941</t>
+          <t>19087</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39558</t>
+          <t>40082</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>58181</t>
+          <t>56907</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>89083</t>
+          <t>90447</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35846</t>
+          <t>36935</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>61793</t>
+          <t>62696</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>100759</t>
+          <t>100455</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>144292</t>
+          <t>140325</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>20,7%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81370</t>
+          <t>80722</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119376</t>
+          <t>119016</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54948</t>
+          <t>55018</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83807</t>
+          <t>85651</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>146350</t>
+          <t>143219</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>195208</t>
+          <t>191003</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>177901</t>
+          <t>177765</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>221638</t>
+          <t>219671</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>110881</t>
+          <t>109636</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>143597</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>300421</t>
+          <t>300578</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>354020</t>
+          <t>356532</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,6%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7063</t>
+          <t>7050</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21798</t>
+          <t>21954</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>5813</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19790</t>
+          <t>21265</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15757</t>
+          <t>16262</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35624</t>
+          <t>36654</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9255</t>
+          <t>9539</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26374</t>
+          <t>27265</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10993</t>
+          <t>11569</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12973</t>
+          <t>13521</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33653</t>
+          <t>34595</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31544</t>
+          <t>31354</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>57915</t>
+          <t>57105</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26903</t>
+          <t>27324</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>50975</t>
+          <t>52288</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>63408</t>
+          <t>63939</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>99968</t>
+          <t>101660</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45926</t>
+          <t>45531</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73907</t>
+          <t>75065</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42368</t>
+          <t>41263</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67783</t>
+          <t>69754</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>95945</t>
+          <t>95876</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>135198</t>
+          <t>134063</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,2%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>170559</t>
+          <t>169284</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>206528</t>
+          <t>206726</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>86670</t>
+          <t>88655</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>116766</t>
+          <t>117753</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>267967</t>
+          <t>266561</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>316246</t>
+          <t>314158</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,05%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9373</t>
+          <t>9452</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26156</t>
+          <t>26052</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5827</t>
+          <t>5865</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20835</t>
+          <t>19620</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18431</t>
+          <t>18905</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39487</t>
+          <t>40358</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9335</t>
+          <t>9653</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25803</t>
+          <t>25610</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>21479</t>
+          <t>22035</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19483</t>
+          <t>19685</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>41448</t>
+          <t>40545</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>55721</t>
+          <t>56315</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>87893</t>
+          <t>87318</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>44492</t>
+          <t>45275</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>72356</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>110847</t>
+          <t>109624</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>152916</t>
+          <t>152566</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>106053</t>
+          <t>107779</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>144367</t>
+          <t>143451</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>58219</t>
+          <t>58691</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>89014</t>
+          <t>90510</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>173093</t>
+          <t>174964</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>222290</t>
+          <t>223578</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,13%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>169077</t>
+          <t>168197</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>209966</t>
+          <t>209757</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>127703</t>
+          <t>127494</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>161484</t>
+          <t>162844</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>307184</t>
+          <t>307104</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>362092</t>
+          <t>362756</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>50,51%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>44908</t>
+          <t>45490</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>76263</t>
+          <t>75840</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>30812</t>
+          <t>31526</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>56963</t>
+          <t>58312</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>83702</t>
+          <t>84245</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>123871</t>
+          <t>125607</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>50221</t>
+          <t>50751</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>82990</t>
+          <t>85568</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28392</t>
+          <t>28139</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>55327</t>
+          <t>55068</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>84691</t>
+          <t>85882</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>126713</t>
+          <t>129736</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>198243</t>
+          <t>197806</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>255103</t>
+          <t>253934</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>139925</t>
+          <t>139050</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>187853</t>
+          <t>187434</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>351183</t>
+          <t>348875</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>429729</t>
+          <t>420571</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>297758</t>
+          <t>303730</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>365939</t>
+          <t>370714</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>216212</t>
+          <t>214922</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>277087</t>
+          <t>270920</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>536587</t>
+          <t>535360</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>625118</t>
+          <t>622905</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,42%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>695358</t>
+          <t>690323</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>772978</t>
+          <t>768325</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>416587</t>
+          <t>420656</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>482083</t>
+          <t>484486</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1131316</t>
+          <t>1131288</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1232799</t>
+          <t>1235484</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,41%</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo requiere que tenga iniciativa en 2016</t>
+          <t>Población según si su trabajo requiere que tenga iniciativa en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7538</t>
+          <t>7657</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23040</t>
+          <t>22422</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>7753</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21794</t>
+          <t>21679</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18200</t>
+          <t>17483</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38194</t>
+          <t>39104</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19845</t>
+          <t>19321</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40444</t>
+          <t>39061</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11828</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28737</t>
+          <t>28465</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35484</t>
+          <t>35285</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60397</t>
+          <t>61312</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28769</t>
+          <t>29208</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51853</t>
+          <t>52487</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25735</t>
+          <t>25942</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45313</t>
+          <t>45917</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>61709</t>
+          <t>60101</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>90876</t>
+          <t>90949</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68988</t>
+          <t>68511</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>98543</t>
+          <t>99112</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35646</t>
+          <t>36554</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58953</t>
+          <t>58308</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>111402</t>
+          <t>114658</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>150323</t>
+          <t>150460</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,64%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63391</t>
+          <t>63357</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>94276</t>
+          <t>92702</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40129</t>
+          <t>40587</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>64564</t>
+          <t>64114</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>111040</t>
+          <t>111681</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>149852</t>
+          <t>149628</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,44%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17396</t>
+          <t>18019</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>7499</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24113</t>
+          <t>23411</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15957</t>
+          <t>15392</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35693</t>
+          <t>35038</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20558</t>
+          <t>20363</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42085</t>
+          <t>43655</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16437</t>
+          <t>16243</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34506</t>
+          <t>35093</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5218,47 +5218,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>5,93%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>12,82%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>54510</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>41259</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>71488</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>7,93%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>6,0%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>12,6%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>54510</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>41262</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>69903</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>6,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>72956</t>
+          <t>71540</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>107785</t>
+          <t>105453</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45014</t>
+          <t>44121</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>72663</t>
+          <t>71857</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>122905</t>
+          <t>124137</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>165849</t>
+          <t>167570</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95360</t>
+          <t>94350</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>133863</t>
+          <t>132772</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56941</t>
+          <t>56416</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84976</t>
+          <t>84316</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>163926</t>
+          <t>161293</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>207767</t>
+          <t>207393</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,15%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>152632</t>
+          <t>152839</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>194755</t>
+          <t>195660</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>93132</t>
+          <t>93492</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>124458</t>
+          <t>125758</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>256302</t>
+          <t>254578</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>306939</t>
+          <t>308271</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,82%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17855</t>
+          <t>17692</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38993</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>7412</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23024</t>
+          <t>22155</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29286</t>
+          <t>28834</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54939</t>
+          <t>55890</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28287</t>
+          <t>27910</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52795</t>
+          <t>52855</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29304</t>
+          <t>28781</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51785</t>
+          <t>52557</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>64738</t>
+          <t>64657</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>101193</t>
+          <t>97799</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>91092</t>
+          <t>90100</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>127314</t>
+          <t>127123</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>62802</t>
+          <t>62420</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>91364</t>
+          <t>90602</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>161968</t>
+          <t>160489</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>207197</t>
+          <t>208084</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,8%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77634</t>
+          <t>75887</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>112520</t>
+          <t>112225</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54152</t>
+          <t>52416</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82186</t>
+          <t>80021</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>140439</t>
+          <t>139956</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>182763</t>
+          <t>183368</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,91%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>78089</t>
+          <t>78104</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>113660</t>
+          <t>112522</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62226</t>
+          <t>60808</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>90913</t>
+          <t>90584</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>149670</t>
+          <t>151205</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>195478</t>
+          <t>196755</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,02%</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>11759</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29594</t>
+          <t>29181</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9361</t>
+          <t>9082</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26070</t>
+          <t>25827</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24730</t>
+          <t>24796</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48772</t>
+          <t>47732</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -6532,12 +6532,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15812</t>
+          <t>16206</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35401</t>
+          <t>36298</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6547,12 +6547,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12144</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>29325</t>
+          <t>29280</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>33766</t>
+          <t>32749</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>58517</t>
+          <t>58401</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6617,12 +6617,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>57729</t>
+          <t>57076</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>86950</t>
+          <t>86749</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>48564</t>
+          <t>50284</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>77010</t>
+          <t>77783</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>116240</t>
+          <t>116334</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>159219</t>
+          <t>157389</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,66%</t>
         </is>
       </c>
     </row>
@@ -6758,12 +6758,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>83415</t>
+          <t>82889</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>119065</t>
+          <t>120206</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>80401</t>
+          <t>78669</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>112502</t>
+          <t>113144</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6808,12 +6808,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>172422</t>
+          <t>174489</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>222240</t>
+          <t>223047</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6843,12 +6843,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,7%</t>
         </is>
       </c>
     </row>
@@ -6871,12 +6871,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>166711</t>
+          <t>163521</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>204335</t>
+          <t>203763</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>114257</t>
+          <t>115069</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>150215</t>
+          <t>150356</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6941,12 +6941,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>288506</t>
+          <t>285979</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>341925</t>
+          <t>339615</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>46,74%</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>53024</t>
+          <t>51619</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>85565</t>
+          <t>86108</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>44422</t>
+          <t>43798</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>74051</t>
+          <t>74665</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>104357</t>
+          <t>105542</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>149534</t>
+          <t>150354</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>102562</t>
+          <t>102552</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>148351</t>
+          <t>146198</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>84348</t>
+          <t>83913</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>122642</t>
+          <t>120147</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7264,47 +7264,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
+          <t>8,09%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>11,58%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>225454</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>200005</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>256263</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>8,13%</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>11,82%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>225454</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>198031</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>256569</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>8,05%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -7327,12 +7327,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>279019</t>
+          <t>277644</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>340812</t>
+          <t>342219</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>202914</t>
+          <t>204091</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>256265</t>
+          <t>257401</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>496863</t>
+          <t>501122</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>579647</t>
+          <t>587496</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,89%</t>
         </is>
       </c>
     </row>
@@ -7440,12 +7440,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>359026</t>
+          <t>359690</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>426156</t>
+          <t>425206</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7455,12 +7455,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>250976</t>
+          <t>251409</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>306827</t>
+          <t>310178</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7510,12 +7510,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>629701</t>
+          <t>626956</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>719610</t>
+          <t>720969</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -7553,12 +7553,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>493187</t>
+          <t>494012</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>566456</t>
+          <t>566863</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7568,12 +7568,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>339872</t>
+          <t>338875</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>395734</t>
+          <t>398800</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>849429</t>
+          <t>847458</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>946415</t>
+          <t>945711</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,45%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6712-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6712-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4847</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17498</t>
+          <t>17556</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14020</t>
+          <t>13517</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>9454</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26143</t>
+          <t>25920</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9048</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25216</t>
+          <t>25671</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20684</t>
+          <t>19661</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17619</t>
+          <t>17537</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39273</t>
+          <t>38796</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26948</t>
+          <t>25911</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50874</t>
+          <t>49179</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10221</t>
+          <t>10204</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26206</t>
+          <t>26065</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41188</t>
+          <t>41487</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>69796</t>
+          <t>69472</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38354</t>
+          <t>38927</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64197</t>
+          <t>64175</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36320</t>
+          <t>35604</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60760</t>
+          <t>60281</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82454</t>
+          <t>82562</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116613</t>
+          <t>117329</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,34%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>138654</t>
+          <t>140367</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>173086</t>
+          <t>171934</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>65130</t>
+          <t>63514</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91031</t>
+          <t>90208</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>214862</t>
+          <t>212916</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>254974</t>
+          <t>252844</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>58,91%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13152</t>
+          <t>12488</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31378</t>
+          <t>32142</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7143</t>
+          <t>6404</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20871</t>
+          <t>21855</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23742</t>
+          <t>23960</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46640</t>
+          <t>47681</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10640</t>
+          <t>10699</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27385</t>
+          <t>28041</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5679</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19310</t>
+          <t>18976</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19087</t>
+          <t>19198</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>40082</t>
+          <t>40880</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56907</t>
+          <t>58181</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>90447</t>
+          <t>90349</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36935</t>
+          <t>36145</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62696</t>
+          <t>62319</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>100455</t>
+          <t>100531</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>140325</t>
+          <t>141180</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80722</t>
+          <t>82335</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119016</t>
+          <t>117050</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55018</t>
+          <t>54340</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85651</t>
+          <t>82679</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>143219</t>
+          <t>145200</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>191003</t>
+          <t>192017</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,33%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>177765</t>
+          <t>176879</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>219671</t>
+          <t>218585</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>109636</t>
+          <t>111334</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>143597</t>
+          <t>145209</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>300578</t>
+          <t>301056</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>356532</t>
+          <t>352152</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>51,95%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7050</t>
+          <t>7670</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21954</t>
+          <t>22213</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21265</t>
+          <t>18759</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16262</t>
+          <t>15676</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36654</t>
+          <t>36885</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9539</t>
+          <t>9726</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27265</t>
+          <t>28882</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11569</t>
+          <t>11408</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13521</t>
+          <t>13227</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34595</t>
+          <t>34432</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31354</t>
+          <t>31998</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>57105</t>
+          <t>58296</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27324</t>
+          <t>26340</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>52288</t>
+          <t>52447</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>63939</t>
+          <t>65437</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>101660</t>
+          <t>101776</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45531</t>
+          <t>46198</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>75065</t>
+          <t>74565</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41263</t>
+          <t>41783</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69754</t>
+          <t>68119</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>95876</t>
+          <t>94186</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>134063</t>
+          <t>132502</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>169284</t>
+          <t>168719</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>206726</t>
+          <t>205568</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>88655</t>
+          <t>86228</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>117753</t>
+          <t>117020</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>266561</t>
+          <t>265292</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>314158</t>
+          <t>315091</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,22%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9452</t>
+          <t>9461</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26052</t>
+          <t>26381</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>5920</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19620</t>
+          <t>19658</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18905</t>
+          <t>18515</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40358</t>
+          <t>39651</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9653</t>
+          <t>9378</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25610</t>
+          <t>25858</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6829</t>
+          <t>6879</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22035</t>
+          <t>23471</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19685</t>
+          <t>18770</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>40545</t>
+          <t>40585</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>56315</t>
+          <t>56497</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>87318</t>
+          <t>87807</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>45275</t>
+          <t>45712</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>72356</t>
+          <t>74011</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>109624</t>
+          <t>112198</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>152566</t>
+          <t>154368</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>107779</t>
+          <t>105427</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>143451</t>
+          <t>144925</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>58691</t>
+          <t>60151</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>90510</t>
+          <t>90632</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>174964</t>
+          <t>173333</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>223578</t>
+          <t>222213</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>30,94%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>168197</t>
+          <t>169472</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>209757</t>
+          <t>211912</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>127494</t>
+          <t>126669</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>162844</t>
+          <t>161248</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>307104</t>
+          <t>306163</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>362756</t>
+          <t>361438</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,32%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>45490</t>
+          <t>46437</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>75840</t>
+          <t>75420</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>31526</t>
+          <t>31560</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>58312</t>
+          <t>57718</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>84245</t>
+          <t>83713</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>125607</t>
+          <t>123935</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>50751</t>
+          <t>52442</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>85568</t>
+          <t>86036</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28139</t>
+          <t>28651</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>55068</t>
+          <t>54074</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>85882</t>
+          <t>88348</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>129736</t>
+          <t>129942</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>197806</t>
+          <t>196914</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>253934</t>
+          <t>252250</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>139050</t>
+          <t>141465</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>187434</t>
+          <t>188814</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>348875</t>
+          <t>347921</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>420571</t>
+          <t>425094</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>303730</t>
+          <t>302679</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>370714</t>
+          <t>367110</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>214922</t>
+          <t>218695</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>270920</t>
+          <t>274046</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>535360</t>
+          <t>538478</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>622905</t>
+          <t>626723</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>690323</t>
+          <t>692765</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>768325</t>
+          <t>769119</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>420656</t>
+          <t>419379</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>484486</t>
+          <t>482649</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1131288</t>
+          <t>1131563</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1235484</t>
+          <t>1236458</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,45%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7657</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22422</t>
+          <t>22092</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7753</t>
+          <t>7839</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21679</t>
+          <t>21875</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17483</t>
+          <t>18463</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39104</t>
+          <t>37960</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19321</t>
+          <t>19253</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39061</t>
+          <t>40666</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11823</t>
+          <t>12644</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28465</t>
+          <t>28456</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35285</t>
+          <t>35496</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61312</t>
+          <t>60948</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29208</t>
+          <t>28463</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52487</t>
+          <t>52237</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25942</t>
+          <t>26156</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45917</t>
+          <t>46128</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>60101</t>
+          <t>61007</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>90949</t>
+          <t>92617</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68511</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>99112</t>
+          <t>98742</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36554</t>
+          <t>36058</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58308</t>
+          <t>58812</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>114658</t>
+          <t>113638</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>150460</t>
+          <t>150819</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,73%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63357</t>
+          <t>64756</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92702</t>
+          <t>92567</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40587</t>
+          <t>40554</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>64114</t>
+          <t>62891</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>111681</t>
+          <t>112383</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>149628</t>
+          <t>148776</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,23%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>4313</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18019</t>
+          <t>17118</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7499</t>
+          <t>8094</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23411</t>
+          <t>23708</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15392</t>
+          <t>15576</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35038</t>
+          <t>35502</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20363</t>
+          <t>19605</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43655</t>
+          <t>42610</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16243</t>
+          <t>17093</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35093</t>
+          <t>35659</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41259</t>
+          <t>41294</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>71488</t>
+          <t>69894</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>71540</t>
+          <t>71071</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>105453</t>
+          <t>106081</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44121</t>
+          <t>43697</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71857</t>
+          <t>70704</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>124137</t>
+          <t>125218</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>167570</t>
+          <t>167140</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94350</t>
+          <t>96809</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>132772</t>
+          <t>133494</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56416</t>
+          <t>56403</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84316</t>
+          <t>84403</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>161293</t>
+          <t>158857</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>207393</t>
+          <t>206662</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>152839</t>
+          <t>153207</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>195660</t>
+          <t>195013</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>93492</t>
+          <t>94088</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>125758</t>
+          <t>126681</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>254578</t>
+          <t>254390</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>308271</t>
+          <t>306822</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,61%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17692</t>
+          <t>17778</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38950</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7412</t>
+          <t>7602</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22155</t>
+          <t>22357</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28834</t>
+          <t>29517</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55890</t>
+          <t>54019</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27910</t>
+          <t>29399</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52855</t>
+          <t>53936</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28781</t>
+          <t>28788</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52557</t>
+          <t>51798</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>64657</t>
+          <t>62460</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>97799</t>
+          <t>97152</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90100</t>
+          <t>90771</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>127123</t>
+          <t>128020</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>62420</t>
+          <t>62646</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>90602</t>
+          <t>91475</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>160489</t>
+          <t>162205</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>208084</t>
+          <t>209777</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>33,07%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>75887</t>
+          <t>77522</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>112225</t>
+          <t>111997</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52416</t>
+          <t>52386</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>80021</t>
+          <t>80312</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>139956</t>
+          <t>138444</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>183368</t>
+          <t>184305</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,05%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>78104</t>
+          <t>78002</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>112522</t>
+          <t>115048</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60808</t>
+          <t>60869</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>90584</t>
+          <t>90585</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>151205</t>
+          <t>149424</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>196755</t>
+          <t>193661</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,53%</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11759</t>
+          <t>11439</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29181</t>
+          <t>29673</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9082</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25827</t>
+          <t>26134</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24796</t>
+          <t>23909</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>47732</t>
+          <t>47832</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -6532,12 +6532,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16206</t>
+          <t>16330</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>36298</t>
+          <t>35330</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6547,12 +6547,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11977</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>29280</t>
+          <t>29093</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>32749</t>
+          <t>33076</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>58401</t>
+          <t>57584</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6617,12 +6617,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>57076</t>
+          <t>58127</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>86749</t>
+          <t>87553</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>50284</t>
+          <t>48964</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>77783</t>
+          <t>78132</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>116334</t>
+          <t>114899</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>157389</t>
+          <t>157912</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,73%</t>
         </is>
       </c>
     </row>
@@ -6758,12 +6758,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>82889</t>
+          <t>84760</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>120206</t>
+          <t>119209</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>78669</t>
+          <t>78597</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>113144</t>
+          <t>111713</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6808,12 +6808,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>174489</t>
+          <t>174464</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>223047</t>
+          <t>221829</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,53%</t>
         </is>
       </c>
     </row>
@@ -6871,12 +6871,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>163521</t>
+          <t>163709</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>203763</t>
+          <t>204061</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>115069</t>
+          <t>114109</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>150356</t>
+          <t>150138</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6941,12 +6941,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>285979</t>
+          <t>288605</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>339615</t>
+          <t>340695</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,89%</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>51619</t>
+          <t>54016</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>86108</t>
+          <t>88525</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>43798</t>
+          <t>45010</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>74665</t>
+          <t>74000</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>105542</t>
+          <t>104826</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>150354</t>
+          <t>147456</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>102552</t>
+          <t>103918</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>146198</t>
+          <t>144669</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>83913</t>
+          <t>83523</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>120147</t>
+          <t>121457</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>200005</t>
+          <t>197916</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>256263</t>
+          <t>255823</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -7327,12 +7327,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>277644</t>
+          <t>275076</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>342219</t>
+          <t>341572</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>204091</t>
+          <t>204281</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>257401</t>
+          <t>255659</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>501122</t>
+          <t>497493</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>587496</t>
+          <t>579444</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,56%</t>
         </is>
       </c>
     </row>
@@ -7440,12 +7440,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>359690</t>
+          <t>359997</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>425206</t>
+          <t>422348</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7455,12 +7455,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>251409</t>
+          <t>250287</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>310178</t>
+          <t>308100</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7510,12 +7510,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>626956</t>
+          <t>625388</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>720969</t>
+          <t>713647</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,02%</t>
         </is>
       </c>
     </row>
@@ -7553,12 +7553,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>494012</t>
+          <t>494847</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>566863</t>
+          <t>567744</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7568,12 +7568,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>338875</t>
+          <t>338261</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>398800</t>
+          <t>399826</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>847458</t>
+          <t>848788</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>945711</t>
+          <t>951257</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,68%</t>
         </is>
       </c>
     </row>
